--- a/data/trans_dic/P8_2_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P8_2_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a subir varios pisos</t>
+          <t>Población con limitación a subir varios pisos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,84; 20,24</t>
+          <t>11,57; 19,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,09; 20,95</t>
+          <t>11,86; 20,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,82; 23,13</t>
+          <t>13,66; 22,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,93; 18,8</t>
+          <t>10,77; 18,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,4; 24,21</t>
+          <t>14,15; 24,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,52; 31,99</t>
+          <t>21,68; 32,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,64; 32,24</t>
+          <t>21,97; 32,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,3; 23,15</t>
+          <t>16,05; 23,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,11; 20,67</t>
+          <t>13,95; 21,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,14; 24,82</t>
+          <t>18,0; 24,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,98; 26,43</t>
+          <t>18,99; 26,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,44; 19,47</t>
+          <t>14,38; 19,52</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,65; 17,17</t>
+          <t>10,94; 17,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,84; 18,96</t>
+          <t>11,92; 18,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,23; 15,04</t>
+          <t>9,09; 14,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,96; 22,54</t>
+          <t>14,61; 22,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,92; 28,48</t>
+          <t>21,18; 28,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,89; 29,6</t>
+          <t>21,62; 29,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,7; 25,7</t>
+          <t>17,97; 25,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,37; 27,7</t>
+          <t>21,94; 27,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,45; 21,55</t>
+          <t>16,69; 21,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,42; 23,15</t>
+          <t>17,76; 23,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,33; 19,24</t>
+          <t>14,45; 19,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,22; 23,91</t>
+          <t>19,12; 24,09</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 15,44</t>
+          <t>8,35; 15,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,89; 20,73</t>
+          <t>12,11; 21,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,94; 16,93</t>
+          <t>9,87; 16,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,29; 18,11</t>
+          <t>11,22; 18,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,91; 30,08</t>
+          <t>20,9; 29,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 28,16</t>
+          <t>18,6; 28,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,48; 24,05</t>
+          <t>14,84; 23,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,21; 22,43</t>
+          <t>16,22; 22,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,99; 22,03</t>
+          <t>15,71; 21,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,59; 22,79</t>
+          <t>16,81; 23,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 19,24</t>
+          <t>13,06; 18,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,67; 19,11</t>
+          <t>14,7; 19,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 16,56</t>
+          <t>9,57; 16,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,22; 20,51</t>
+          <t>11,98; 19,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,69; 18,91</t>
+          <t>11,67; 19,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,25; 23,48</t>
+          <t>14,31; 23,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,51; 27,89</t>
+          <t>19,1; 27,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,43; 36,14</t>
+          <t>26,63; 36,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,85; 31,56</t>
+          <t>21,77; 31,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 21,99</t>
+          <t>10,28; 22,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,42; 21,33</t>
+          <t>15,36; 20,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,88; 27,09</t>
+          <t>20,38; 26,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,81; 24,4</t>
+          <t>17,67; 24,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,87; 21,07</t>
+          <t>12,76; 20,95</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 13,77</t>
+          <t>6,21; 14,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,61; 23,22</t>
+          <t>12,33; 23,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 17,34</t>
+          <t>8,97; 17,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,93; 16,25</t>
+          <t>9,21; 16,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,27; 24,8</t>
+          <t>13,88; 24,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,42; 37,2</t>
+          <t>24,38; 37,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,53; 27,7</t>
+          <t>17,02; 28,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,55; 28,07</t>
+          <t>11,46; 28,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,91; 17,65</t>
+          <t>10,91; 17,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,0; 28,72</t>
+          <t>20,2; 28,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,11; 21,53</t>
+          <t>14,13; 21,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,98; 21,56</t>
+          <t>12,35; 21,55</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,51; 20,46</t>
+          <t>11,46; 20,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,48; 24,93</t>
+          <t>15,8; 25,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,88; 25,97</t>
+          <t>15,96; 25,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,99; 15,81</t>
+          <t>10,18; 16,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,71; 31,42</t>
+          <t>20,33; 30,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,58; 33,39</t>
+          <t>23,51; 34,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,11; 35,89</t>
+          <t>25,17; 36,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,33; 23,01</t>
+          <t>16,44; 23,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,55; 24,27</t>
+          <t>17,47; 24,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,79; 28,04</t>
+          <t>20,86; 27,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,78; 29,91</t>
+          <t>21,69; 29,48</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,82; 18,23</t>
+          <t>13,92; 18,5</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,92; 18,43</t>
+          <t>12,82; 18,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,36; 15,93</t>
+          <t>10,17; 15,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,37; 19,66</t>
+          <t>13,44; 19,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,47; 19,75</t>
+          <t>13,49; 19,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,93; 26,34</t>
+          <t>20,0; 26,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,84; 28,81</t>
+          <t>21,96; 28,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,95; 26,56</t>
+          <t>19,89; 26,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,8; 25,86</t>
+          <t>9,09; 26,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,22; 21,69</t>
+          <t>17,23; 21,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,12; 21,58</t>
+          <t>16,89; 21,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,71; 22,49</t>
+          <t>17,69; 22,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,09; 21,58</t>
+          <t>11,69; 21,58</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,24; 17,3</t>
+          <t>12,09; 17,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,36; 19,09</t>
+          <t>13,37; 19,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,2; 14,79</t>
+          <t>10,09; 14,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,32; 71,65</t>
+          <t>12,11; 71,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,46; 26,45</t>
+          <t>20,64; 26,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,22; 25,05</t>
+          <t>19,1; 24,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,77; 22,59</t>
+          <t>16,94; 22,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,41; 26,91</t>
+          <t>21,42; 26,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,3; 21,16</t>
+          <t>17,1; 21,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17,25; 21,33</t>
+          <t>17,29; 21,31</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,14; 18,03</t>
+          <t>13,92; 17,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,05; 57,0</t>
+          <t>17,95; 56,75</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,84; 15,12</t>
+          <t>12,7; 15,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,38; 16,92</t>
+          <t>14,25; 16,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,3; 15,8</t>
+          <t>13,24; 15,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,82; 38,42</t>
+          <t>14,81; 38,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,77; 24,82</t>
+          <t>21,82; 24,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,1; 27,25</t>
+          <t>24,27; 27,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,43; 24,37</t>
+          <t>21,44; 24,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,9; 22,73</t>
+          <t>16,86; 22,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,7; 19,68</t>
+          <t>17,73; 19,57</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,75; 21,65</t>
+          <t>19,78; 21,71</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,69; 19,71</t>
+          <t>17,73; 19,68</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,73; 31,44</t>
+          <t>17,66; 29,04</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a subir varios pisos</t>
+          <t>Población con limitación a subir varios pisos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32321; 55260</t>
+          <t>31577; 54356</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35641; 61756</t>
+          <t>34954; 60087</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40609; 67941</t>
+          <t>40121; 66739</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34030; 58548</t>
+          <t>33553; 58634</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37569; 63161</t>
+          <t>36897; 62742</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61829; 91879</t>
+          <t>62261; 92930</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62466; 93086</t>
+          <t>63432; 94608</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47199; 67050</t>
+          <t>46473; 66901</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>75337; 110334</t>
+          <t>74477; 112335</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105557; 144423</t>
+          <t>104734; 143504</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>110538; 153953</t>
+          <t>110624; 153170</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86782; 117045</t>
+          <t>86409; 117333</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52526; 84650</t>
+          <t>53942; 85197</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59878; 95840</t>
+          <t>60263; 94835</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46406; 75603</t>
+          <t>45704; 74013</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77547; 116840</t>
+          <t>75730; 115211</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>105440; 143539</t>
+          <t>106729; 144241</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>114649; 155045</t>
+          <t>113218; 155476</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92591; 134439</t>
+          <t>94015; 132592</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>110041; 142666</t>
+          <t>113003; 143182</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>164024; 214870</t>
+          <t>166385; 215850</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>179314; 238293</t>
+          <t>182841; 237194</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146990; 197300</t>
+          <t>148208; 197831</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>198576; 247030</t>
+          <t>197581; 248939</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26523; 49236</t>
+          <t>26617; 49120</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38516; 67175</t>
+          <t>39247; 68187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31654; 53925</t>
+          <t>31449; 52298</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35687; 57239</t>
+          <t>35468; 57269</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>70128; 100895</t>
+          <t>70116; 100472</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64097; 96035</t>
+          <t>63429; 96786</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48689; 80872</t>
+          <t>49922; 80258</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56507; 78171</t>
+          <t>56522; 78474</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>104638; 144119</t>
+          <t>102783; 141986</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110345; 151544</t>
+          <t>111820; 153117</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88536; 125967</t>
+          <t>85548; 124210</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97523; 126979</t>
+          <t>97696; 127646</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33924; 59411</t>
+          <t>34334; 58130</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45683; 76695</t>
+          <t>44819; 74216</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43255; 69978</t>
+          <t>43181; 72353</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44533; 73387</t>
+          <t>44724; 73460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72475; 103590</t>
+          <t>70958; 102747</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>102788; 140573</t>
+          <t>103581; 141406</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84632; 122219</t>
+          <t>84329; 121484</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47789; 104630</t>
+          <t>48923; 107044</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>112574; 155764</t>
+          <t>112142; 152566</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>159287; 206712</t>
+          <t>155450; 203494</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>134829; 184782</t>
+          <t>133784; 182349</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>101487; 166070</t>
+          <t>100621; 165172</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11935; 27998</t>
+          <t>12635; 28601</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26806; 49367</t>
+          <t>26206; 50070</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18222; 36629</t>
+          <t>18939; 37399</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15953; 29046</t>
+          <t>16461; 29367</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27559; 51498</t>
+          <t>28830; 50998</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53618; 81678</t>
+          <t>53545; 83033</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36124; 60550</t>
+          <t>37208; 61433</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29816; 72495</t>
+          <t>29590; 73677</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44847; 72540</t>
+          <t>44838; 73789</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86456; 124145</t>
+          <t>87292; 122945</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60667; 92533</t>
+          <t>60730; 91244</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52370; 94213</t>
+          <t>53957; 94179</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31159; 55419</t>
+          <t>31031; 54900</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42405; 68306</t>
+          <t>43300; 68962</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41796; 68345</t>
+          <t>41987; 68241</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26940; 42639</t>
+          <t>27459; 43521</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>57608; 87379</t>
+          <t>56551; 85608</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62979; 93147</t>
+          <t>65569; 96256</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65861; 98012</t>
+          <t>68730; 98508</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>41983; 59157</t>
+          <t>42252; 60019</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96360; 133210</t>
+          <t>95909; 131925</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>114940; 155037</t>
+          <t>115320; 154238</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>116782; 160365</t>
+          <t>116301; 158089</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>72806; 96001</t>
+          <t>73299; 97440</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>79457; 113325</t>
+          <t>78820; 112733</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>68366; 105136</t>
+          <t>67120; 103547</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87789; 129054</t>
+          <t>88232; 127916</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83994; 123152</t>
+          <t>84089; 122965</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>127218; 168115</t>
+          <t>127639; 170685</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>151519; 199869</t>
+          <t>152336; 197248</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>137935; 183593</t>
+          <t>137507; 184620</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>83216; 219580</t>
+          <t>77239; 220996</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>215826; 271874</t>
+          <t>215988; 268895</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>231752; 292088</t>
+          <t>228693; 289166</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>238713; 303127</t>
+          <t>238369; 297932</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>163278; 317771</t>
+          <t>172131; 317809</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>91071; 128674</t>
+          <t>89899; 126823</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>103984; 148542</t>
+          <t>104051; 148830</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>79381; 115176</t>
+          <t>78535; 113984</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>114454; 665411</t>
+          <t>112422; 659594</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>160308; 207270</t>
+          <t>161728; 210899</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>158372; 206400</t>
+          <t>157335; 205632</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>138536; 186632</t>
+          <t>139948; 188015</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>153677; 193159</t>
+          <t>153733; 192472</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>264290; 323206</t>
+          <t>261207; 325327</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>276252; 341701</t>
+          <t>276911; 341353</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>226848; 289302</t>
+          <t>223354; 283832</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>297195; 938463</t>
+          <t>295530; 934402</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>420700; 495339</t>
+          <t>416239; 495773</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>492333; 579094</t>
+          <t>487710; 575578</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>451351; 536199</t>
+          <t>449509; 537346</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>512669; 1328973</t>
+          <t>512202; 1322235</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>735747; 838704</t>
+          <t>737279; 836512</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>857459; 969377</t>
+          <t>863317; 968987</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>759547; 863753</t>
+          <t>760064; 861693</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>627069; 843638</t>
+          <t>625698; 843437</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1178324; 1310043</t>
+          <t>1180066; 1302736</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1378450; 1511431</t>
+          <t>1380738; 1515148</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1227561; 1367649</t>
+          <t>1230276; 1365649</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1271347; 2254535</t>
+          <t>1265988; 2082517</t>
         </is>
       </c>
     </row>
